--- a/data/stats/supp_tables/spweedcountsPERENN-cc-pairs.xlsx
+++ b/data/stats/supp_tables/spweedcountsPERENN-cc-pairs.xlsx
@@ -428,16 +428,16 @@
         </is>
       </c>
       <c r="E2">
-        <v>4.059252933785729E-16</v>
+        <v>1.375392855162971E-13</v>
       </c>
       <c r="F2">
-        <v>0.3828672789229691</v>
+        <v>0.3828672319049061</v>
       </c>
       <c r="G2">
-        <v>354</v>
+        <v>159.9999999999862</v>
       </c>
       <c r="H2">
-        <v>1.060224562726978E-15</v>
+        <v>3.592349359123483E-13</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -470,19 +470,19 @@
         </is>
       </c>
       <c r="E3">
-        <v>-0.1059122325484005</v>
+        <v>-0.1059122325482699</v>
       </c>
       <c r="F3">
-        <v>0.3828672789229688</v>
+        <v>0.3828672319049073</v>
       </c>
       <c r="G3">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H3">
-        <v>-0.2766291045981747</v>
+        <v>-0.2766291385693078</v>
       </c>
       <c r="I3">
-        <v>0.998712979559201</v>
+        <v>0.998704835502116</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="E4">
-        <v>-0.1059122325484007</v>
+        <v>-0.1059122325482629</v>
       </c>
       <c r="F4">
-        <v>0.3828672789229694</v>
+        <v>0.3828672319049063</v>
       </c>
       <c r="G4">
-        <v>354</v>
+        <v>159.9999999999897</v>
       </c>
       <c r="H4">
-        <v>-0.2766291045981747</v>
+        <v>-0.2766291385692902</v>
       </c>
       <c r="I4">
-        <v>0.998712979559201</v>
+        <v>0.9987048355021162</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="E5">
-        <v>3.885780586188048E-16</v>
+        <v>1.303124275153777E-13</v>
       </c>
       <c r="F5">
-        <v>0.3828672789229682</v>
+        <v>0.3828672319049059</v>
       </c>
       <c r="G5">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H5">
-        <v>1.014915820730101E-15</v>
+        <v>3.403593116784252E-13</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -596,19 +596,19 @@
         </is>
       </c>
       <c r="E6">
-        <v>-0.1059122325484009</v>
+        <v>-0.1059122325484075</v>
       </c>
       <c r="F6">
-        <v>0.3828672789229736</v>
+        <v>0.3828672319048937</v>
       </c>
       <c r="G6">
-        <v>354</v>
+        <v>159.9999999999879</v>
       </c>
       <c r="H6">
-        <v>-0.2766291045981724</v>
+        <v>-0.2766291385696769</v>
       </c>
       <c r="I6">
-        <v>0.9987129795592011</v>
+        <v>0.9987048355021091</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="E7">
-        <v>-0.1059122325484011</v>
+        <v>-0.1059122325484005</v>
       </c>
       <c r="F7">
-        <v>0.3828672789229742</v>
+        <v>0.3828672319048937</v>
       </c>
       <c r="G7">
-        <v>354</v>
+        <v>159.9999999999897</v>
       </c>
       <c r="H7">
-        <v>-0.2766291045981723</v>
+        <v>-0.2766291385696586</v>
       </c>
       <c r="I7">
-        <v>0.9987129795592011</v>
+        <v>0.9987048355021095</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="E8">
-        <v>-1.734723475976807E-17</v>
+        <v>-7.226858000919378E-15</v>
       </c>
       <c r="F8">
-        <v>0.3828672789229736</v>
+        <v>0.3828672319048936</v>
       </c>
       <c r="G8">
-        <v>354</v>
+        <v>159.9999999999879</v>
       </c>
       <c r="H8">
-        <v>-4.530874199687887E-17</v>
+        <v>-1.887562423392392E-14</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="E9">
-        <v>-1.52655665885959E-16</v>
+        <v>7.008282842946301E-15</v>
       </c>
       <c r="F9">
-        <v>0.3828672789229741</v>
+        <v>0.3828672319048942</v>
       </c>
       <c r="G9">
-        <v>354</v>
+        <v>159.9999999999879</v>
       </c>
       <c r="H9">
-        <v>-3.987169295725335E-16</v>
+        <v>1.830473401465495E-14</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.1059122325484009</v>
+        <v>0.1059122325484002</v>
       </c>
       <c r="F10">
-        <v>0.3828672789229737</v>
+        <v>0.3828672319048938</v>
       </c>
       <c r="G10">
-        <v>354</v>
+        <v>159.9999999999879</v>
       </c>
       <c r="H10">
-        <v>0.2766291045981722</v>
+        <v>0.276629138569658</v>
       </c>
       <c r="I10">
-        <v>0.9987129795592011</v>
+        <v>0.9987048355021095</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="E11">
-        <v>0.105912232548401</v>
+        <v>0.1059122325483932</v>
       </c>
       <c r="F11">
-        <v>0.382867278922974</v>
+        <v>0.3828672319048937</v>
       </c>
       <c r="G11">
-        <v>354</v>
+        <v>159.9999999999879</v>
       </c>
       <c r="H11">
-        <v>0.2766291045981725</v>
+        <v>0.2766291385696397</v>
       </c>
       <c r="I11">
-        <v>0.9987129795592011</v>
+        <v>0.9987048355021098</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.030097438609814</v>
+        <v>1.030097438609769</v>
       </c>
       <c r="F12">
-        <v>0.3828672789229716</v>
+        <v>0.3828672319048955</v>
       </c>
       <c r="G12">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H12">
-        <v>2.690481781330438</v>
+        <v>2.690482111735397</v>
       </c>
       <c r="I12">
-        <v>0.05735826630261687</v>
+        <v>0.05980503651699709</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="E13">
-        <v>2.080873934969662</v>
+        <v>2.080873934969617</v>
       </c>
       <c r="F13">
-        <v>0.3828672789229708</v>
+        <v>0.3828672319048951</v>
       </c>
       <c r="G13">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H13">
-        <v>5.434974597002094</v>
+        <v>5.43497526444496</v>
       </c>
       <c r="I13">
-        <v>1.016086934590987E-06</v>
+        <v>1.98960256969638E-06</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="E14">
-        <v>1.902046561695743</v>
+        <v>1.9020465616957</v>
       </c>
       <c r="F14">
-        <v>0.3828672789229709</v>
+        <v>0.3828672319048954</v>
       </c>
       <c r="G14">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H14">
-        <v>4.967900539963396</v>
+        <v>4.967901150047154</v>
       </c>
       <c r="I14">
-        <v>1.042045465937669E-05</v>
+        <v>1.691685801308296E-05</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
         </is>
       </c>
       <c r="E15">
-        <v>1.773284794409316</v>
+        <v>1.77328479440927</v>
       </c>
       <c r="F15">
-        <v>0.382867278922971</v>
+        <v>0.3828672319048949</v>
       </c>
       <c r="G15">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H15">
-        <v>4.631591394797889</v>
+        <v>4.631591963581146</v>
       </c>
       <c r="I15">
-        <v>4.997354960323275E-05</v>
+        <v>7.263281653469011E-05</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1019,20 +1019,20 @@
         <v>1.050776496359848</v>
       </c>
       <c r="F16">
-        <v>0.3828672789229723</v>
+        <v>0.3828672319048938</v>
       </c>
       <c r="G16">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H16">
-        <v>2.744492815671641</v>
+        <v>2.744493152709569</v>
       </c>
       <c r="I16">
-        <v>0.04964975296962904</v>
+        <v>0.05196794233349844</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.871949123085929</v>
+        <v>0.8719491230859309</v>
       </c>
       <c r="F17">
-        <v>0.3828672789229726</v>
+        <v>0.3828672319048942</v>
       </c>
       <c r="G17">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H17">
-        <v>2.277418758632943</v>
+        <v>2.277419038311763</v>
       </c>
       <c r="I17">
-        <v>0.1546550843575468</v>
+        <v>0.1576459852330041</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="E18">
-        <v>0.7431873557995013</v>
+        <v>0.7431873557995005</v>
       </c>
       <c r="F18">
-        <v>0.3828672789229725</v>
+        <v>0.3828672319048944</v>
       </c>
       <c r="G18">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H18">
-        <v>1.941109613467439</v>
+        <v>1.941109851845746</v>
       </c>
       <c r="I18">
-        <v>0.2975666291490325</v>
+        <v>0.3000523165686145</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="E19">
-        <v>-0.1788273732739187</v>
+        <v>-0.1788273732739168</v>
       </c>
       <c r="F19">
-        <v>0.3828672789229723</v>
+        <v>0.3828672319048942</v>
       </c>
       <c r="G19">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H19">
-        <v>-0.467074057038696</v>
+        <v>-0.4670741143978033</v>
       </c>
       <c r="I19">
-        <v>0.9902087685443336</v>
+        <v>0.99015517819613</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="E20">
-        <v>-0.3075891405603464</v>
+        <v>-0.3075891405603473</v>
       </c>
       <c r="F20">
-        <v>0.3828672789229722</v>
+        <v>0.3828672319048935</v>
       </c>
       <c r="G20">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H20">
-        <v>-0.803383202204201</v>
+        <v>-0.8033833008638206</v>
       </c>
       <c r="I20">
-        <v>0.9294784064290749</v>
+        <v>0.929252255668082</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1226,19 +1226,19 @@
         </is>
       </c>
       <c r="E21">
-        <v>-0.1287617672864277</v>
+        <v>-0.1287617672864304</v>
       </c>
       <c r="F21">
-        <v>0.3828672789229726</v>
+        <v>0.3828672319048939</v>
       </c>
       <c r="G21">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H21">
-        <v>-0.3363091451655044</v>
+        <v>-0.3363091864660161</v>
       </c>
       <c r="I21">
-        <v>0.9972362037835498</v>
+        <v>0.9972193392274744</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1268,19 +1268,19 @@
         </is>
       </c>
       <c r="E22">
-        <v>1.751330975549327</v>
+        <v>1.751330975549295</v>
       </c>
       <c r="F22">
-        <v>0.3828672789229716</v>
+        <v>0.3828672319048953</v>
       </c>
       <c r="G22">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H22">
-        <v>4.574250848690767</v>
+        <v>4.574251410432344</v>
       </c>
       <c r="I22">
-        <v>6.467854250069571E-05</v>
+        <v>9.242318413438255E-05</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="E23">
-        <v>2.509687546030887</v>
+        <v>2.509687546030856</v>
       </c>
       <c r="F23">
-        <v>0.3828672789229703</v>
+        <v>0.3828672319048955</v>
       </c>
       <c r="G23">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H23">
-        <v>6.554980496350576</v>
+        <v>6.554981301335979</v>
       </c>
       <c r="I23">
-        <v>1.964512441610111E-09</v>
+        <v>7.26680104978783E-09</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="E24">
-        <v>2.004306137551569</v>
+        <v>2.004306137551538</v>
       </c>
       <c r="F24">
-        <v>0.3828672789229706</v>
+        <v>0.3828672319048954</v>
       </c>
       <c r="G24">
-        <v>354</v>
+        <v>160.0000000000078</v>
       </c>
       <c r="H24">
-        <v>5.234989375926316</v>
+        <v>5.234990018809992</v>
       </c>
       <c r="I24">
-        <v>2.811143482550627E-06</v>
+        <v>5.054388129477339E-06</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1394,19 +1394,19 @@
         </is>
       </c>
       <c r="E25">
-        <v>2.509687546030888</v>
+        <v>2.509687546030854</v>
       </c>
       <c r="F25">
-        <v>0.3828672789229709</v>
+        <v>0.3828672319048948</v>
       </c>
       <c r="G25">
-        <v>354</v>
+        <v>160.0000000000095</v>
       </c>
       <c r="H25">
-        <v>6.554980496350569</v>
+        <v>6.554981301335987</v>
       </c>
       <c r="I25">
-        <v>1.964512441610111E-09</v>
+        <v>7.26680104978783E-09</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="E26">
-        <v>0.7583565704815596</v>
+        <v>0.7583565704815611</v>
       </c>
       <c r="F26">
-        <v>0.3828672789229722</v>
+        <v>0.3828672319048946</v>
       </c>
       <c r="G26">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H26">
-        <v>1.980729647659786</v>
+        <v>1.980729890903642</v>
       </c>
       <c r="I26">
-        <v>0.2775379075062523</v>
+        <v>0.2801314051585657</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1478,19 +1478,19 @@
         </is>
       </c>
       <c r="E27">
-        <v>0.252975162002241</v>
+        <v>0.2529751620022438</v>
       </c>
       <c r="F27">
-        <v>0.3828672789229726</v>
+        <v>0.3828672319048947</v>
       </c>
       <c r="G27">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H27">
-        <v>0.6607385272355331</v>
+        <v>0.6607386083776517</v>
       </c>
       <c r="I27">
-        <v>0.9645370608430588</v>
+        <v>0.9643860492297469</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="E28">
-        <v>0.7583565704815601</v>
+        <v>0.7583565704815597</v>
       </c>
       <c r="F28">
-        <v>0.3828672789229726</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G28">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H28">
-        <v>1.980729647659785</v>
+        <v>1.980729890903641</v>
       </c>
       <c r="I28">
-        <v>0.2775379075062525</v>
+        <v>0.2801314051585664</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="E29">
-        <v>-0.5053814084793186</v>
+        <v>-0.5053814084793175</v>
       </c>
       <c r="F29">
-        <v>0.3828672789229718</v>
+        <v>0.3828672319048949</v>
       </c>
       <c r="G29">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H29">
-        <v>-1.319991120424253</v>
+        <v>-1.319991282525989</v>
       </c>
       <c r="I29">
-        <v>0.678947530599599</v>
+        <v>0.6792033863478588</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="E30">
-        <v>5.620504062164855E-16</v>
+        <v>-1.498801083243961E-15</v>
       </c>
       <c r="F30">
-        <v>0.3828672789229718</v>
+        <v>0.3828672319048946</v>
       </c>
       <c r="G30">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H30">
-        <v>1.468003240698882E-15</v>
+        <v>-3.914675789272737E-15</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -1646,19 +1646,19 @@
         </is>
       </c>
       <c r="E31">
-        <v>0.5053814084793191</v>
+        <v>0.5053814084793159</v>
       </c>
       <c r="F31">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048945</v>
       </c>
       <c r="G31">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H31">
-        <v>1.319991120424252</v>
+        <v>1.319991282525986</v>
       </c>
       <c r="I31">
-        <v>0.6789475305995998</v>
+        <v>0.6792033863478604</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="E32">
-        <v>4.336808689942018E-16</v>
+        <v>8.554615349432027E-14</v>
       </c>
       <c r="F32">
-        <v>0.3828672789229763</v>
+        <v>0.3828672319048992</v>
       </c>
       <c r="G32">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H32">
-        <v>1.132718549921964E-15</v>
+        <v>2.234355577224461E-13</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="E33">
-        <v>-1.040834085586084E-16</v>
+        <v>8.126832540256146E-14</v>
       </c>
       <c r="F33">
-        <v>0.3828672789229756</v>
+        <v>0.3828672319048996</v>
       </c>
       <c r="G33">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H33">
-        <v>-2.718524519812719E-16</v>
+        <v>2.122624205738968E-13</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="E34">
-        <v>-9.020562075079397E-17</v>
+        <v>8.408551632754779E-14</v>
       </c>
       <c r="F34">
-        <v>0.3828672789229756</v>
+        <v>0.3828672319048997</v>
       </c>
       <c r="G34">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H34">
-        <v>-2.356054583837689E-16</v>
+        <v>2.196205611778074E-13</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="E35">
-        <v>4.163336342344337E-16</v>
+        <v>7.979727989493313E-14</v>
       </c>
       <c r="F35">
-        <v>0.3828672789229752</v>
+        <v>0.3828672319048995</v>
       </c>
       <c r="G35">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H35">
-        <v>1.087409807925088E-15</v>
+        <v>2.084202387807218E-13</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="E36">
-        <v>-5.377642775528102E-16</v>
+        <v>-4.277828091758806E-15</v>
       </c>
       <c r="F36">
-        <v>0.3828672789229723</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G36">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H36">
-        <v>-1.40457100190325E-15</v>
+        <v>-1.117313714854929E-14</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="E37">
-        <v>-5.238864897449957E-16</v>
+        <v>-1.460637166772472E-15</v>
       </c>
       <c r="F37">
-        <v>0.3828672789229728</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G37">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H37">
-        <v>-1.368324008305745E-15</v>
+        <v>-3.814996544638484E-15</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -1940,16 +1940,16 @@
         </is>
       </c>
       <c r="E38">
-        <v>-1.734723475976807E-17</v>
+        <v>-5.748873599387139E-15</v>
       </c>
       <c r="F38">
-        <v>0.382867278922973</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G38">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H38">
-        <v>-4.530874199687894E-17</v>
+        <v>-1.501531894172439E-14</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="E39">
-        <v>1.387778780781446E-17</v>
+        <v>2.817190924986335E-15</v>
       </c>
       <c r="F39">
-        <v>0.3828672789229725</v>
+        <v>0.3828672319048941</v>
       </c>
       <c r="G39">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H39">
-        <v>3.62469935975032E-17</v>
+        <v>7.358140603910803E-15</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E40">
-        <v>5.204170427930421E-16</v>
+        <v>-1.471045507628332E-15</v>
       </c>
       <c r="F40">
-        <v>0.3828672789229726</v>
+        <v>0.382867231904894</v>
       </c>
       <c r="G40">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H40">
-        <v>1.35926225990637E-15</v>
+        <v>-3.8421817931751E-15</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -2066,16 +2066,16 @@
         </is>
       </c>
       <c r="E41">
-        <v>5.065392549852277E-16</v>
+        <v>-4.288236432614667E-15</v>
       </c>
       <c r="F41">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048946</v>
       </c>
       <c r="G41">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H41">
-        <v>1.323015266308866E-15</v>
+        <v>-1.120032239708589E-14</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -2108,19 +2108,19 @@
         </is>
       </c>
       <c r="E42">
-        <v>1.028956303299167</v>
+        <v>1.02895630329915</v>
       </c>
       <c r="F42">
-        <v>0.382867278922974</v>
+        <v>0.382867231904896</v>
       </c>
       <c r="G42">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H42">
-        <v>2.687501282934587</v>
+        <v>2.687501612973612</v>
       </c>
       <c r="I42">
-        <v>0.05781135018014016</v>
+        <v>0.06026500380373756</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2150,19 +2150,19 @@
         </is>
       </c>
       <c r="E43">
-        <v>1.397165878685016</v>
+        <v>1.397165878685002</v>
       </c>
       <c r="F43">
-        <v>0.3828672789229724</v>
+        <v>0.382867231904896</v>
       </c>
       <c r="G43">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H43">
-        <v>3.649217249944481</v>
+        <v>3.649217698087198</v>
       </c>
       <c r="I43">
-        <v>0.002783946478370658</v>
+        <v>0.00323407382455132</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2192,19 +2192,19 @@
         </is>
       </c>
       <c r="E44">
-        <v>1.22984244268821</v>
+        <v>1.229842442688194</v>
       </c>
       <c r="F44">
-        <v>0.3828672789229736</v>
+        <v>0.3828672319048982</v>
       </c>
       <c r="G44">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H44">
-        <v>3.212189994788334</v>
+        <v>3.212190389261829</v>
       </c>
       <c r="I44">
-        <v>0.01244753650006647</v>
+        <v>0.01361199243137401</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
         </is>
       </c>
       <c r="E45">
-        <v>1.686043873890005</v>
+        <v>1.686043873889991</v>
       </c>
       <c r="F45">
-        <v>0.3828672789229751</v>
+        <v>0.3828672319048965</v>
       </c>
       <c r="G45">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H45">
-        <v>4.403729351416322</v>
+        <v>4.403729892217052</v>
       </c>
       <c r="I45">
-        <v>0.000137002672491171</v>
+        <v>0.0001867081616756527</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2276,19 +2276,19 @@
         </is>
       </c>
       <c r="E46">
-        <v>0.368209575385849</v>
+        <v>0.368209575385852</v>
       </c>
       <c r="F46">
-        <v>0.3828672789229723</v>
+        <v>0.3828672319048935</v>
       </c>
       <c r="G46">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H46">
-        <v>0.9617159670098833</v>
+        <v>0.9617160851135921</v>
       </c>
       <c r="I46">
-        <v>0.8720652656977135</v>
+        <v>0.871814900781262</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2318,19 +2318,19 @@
         </is>
       </c>
       <c r="E47">
-        <v>0.2008861393890432</v>
+        <v>0.2008861393890438</v>
       </c>
       <c r="F47">
-        <v>0.3828672789229717</v>
+        <v>0.3828672319048947</v>
       </c>
       <c r="G47">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H47">
-        <v>0.5246887118537468</v>
+        <v>0.5246887762882368</v>
       </c>
       <c r="I47">
-        <v>0.984815081382534</v>
+        <v>0.9847369757926396</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2360,19 +2360,19 @@
         </is>
       </c>
       <c r="E48">
-        <v>0.6570875705908384</v>
+        <v>0.6570875705908404</v>
       </c>
       <c r="F48">
-        <v>0.3828672789229728</v>
+        <v>0.3828672319048952</v>
       </c>
       <c r="G48">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H48">
-        <v>1.716228068481754</v>
+        <v>1.716228279243448</v>
       </c>
       <c r="I48">
-        <v>0.4252564300541872</v>
+        <v>0.4269567587093018</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2402,19 +2402,19 @@
         </is>
       </c>
       <c r="E49">
-        <v>-0.1673234359968058</v>
+        <v>-0.1673234359968082</v>
       </c>
       <c r="F49">
-        <v>0.3828672789229718</v>
+        <v>0.3828672319048936</v>
       </c>
       <c r="G49">
-        <v>354</v>
+        <v>160.0000000000024</v>
       </c>
       <c r="H49">
-        <v>-0.4370272551561379</v>
+        <v>-0.4370273088253534</v>
       </c>
       <c r="I49">
-        <v>0.9924000902895118</v>
+        <v>0.9923572797095686</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2444,19 +2444,19 @@
         </is>
       </c>
       <c r="E50">
-        <v>0.2888779952049894</v>
+        <v>0.2888779952049885</v>
       </c>
       <c r="F50">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048948</v>
       </c>
       <c r="G50">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H50">
-        <v>0.7545121014718718</v>
+        <v>0.754512194129861</v>
       </c>
       <c r="I50">
-        <v>0.9432230031499732</v>
+        <v>0.9430198504095348</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="E51">
-        <v>0.4562014312017952</v>
+        <v>0.4562014312017967</v>
       </c>
       <c r="F51">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048966</v>
       </c>
       <c r="G51">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H51">
-        <v>1.191539356628009</v>
+        <v>1.191539502955207</v>
       </c>
       <c r="I51">
-        <v>0.7562783463446892</v>
+        <v>0.7562436270749503</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2528,19 +2528,19 @@
         </is>
       </c>
       <c r="E52">
-        <v>0.5753312507747932</v>
+        <v>0.5753312507747743</v>
       </c>
       <c r="F52">
-        <v>0.3828672789229745</v>
+        <v>0.3828672319048966</v>
       </c>
       <c r="G52">
-        <v>354</v>
+        <v>160.0000000000024</v>
       </c>
       <c r="H52">
-        <v>1.502691095444954</v>
+        <v>1.502691279983149</v>
       </c>
       <c r="I52">
-        <v>0.5614023398854942</v>
+        <v>0.5622603056099611</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="E53">
-        <v>0.5325454749639633</v>
+        <v>0.5325454749639461</v>
       </c>
       <c r="F53">
-        <v>0.3828672789229731</v>
+        <v>0.3828672319048966</v>
       </c>
       <c r="G53">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H53">
-        <v>1.390940161985227</v>
+        <v>1.390940332799829</v>
       </c>
       <c r="I53">
-        <v>0.6338994386525321</v>
+        <v>0.6343664135231352</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="E54">
-        <v>0.2653573071346393</v>
+        <v>0.2653573071346201</v>
       </c>
       <c r="F54">
-        <v>0.3828672789229742</v>
+        <v>0.3828672319048978</v>
       </c>
       <c r="G54">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H54">
-        <v>0.6930790948787876</v>
+        <v>0.6930791799924353</v>
       </c>
       <c r="I54">
-        <v>0.9579147254484107</v>
+        <v>0.9577451570860624</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E55">
-        <v>0.294054112340202</v>
+        <v>0.2940541123401846</v>
       </c>
       <c r="F55">
-        <v>0.3828672789229739</v>
+        <v>0.3828672319048976</v>
       </c>
       <c r="G55">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H55">
-        <v>0.768031452485028</v>
+        <v>0.7680315468032174</v>
       </c>
       <c r="I55">
-        <v>0.9396061507674084</v>
+        <v>0.9393961995196641</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2696,19 +2696,19 @@
         </is>
       </c>
       <c r="E56">
-        <v>-0.04278577581082985</v>
+        <v>-0.04278577581082822</v>
       </c>
       <c r="F56">
-        <v>0.3828672789229732</v>
+        <v>0.3828672319048937</v>
       </c>
       <c r="G56">
-        <v>354</v>
+        <v>159.9999999999987</v>
       </c>
       <c r="H56">
-        <v>-0.1117509334597321</v>
+        <v>-0.1117509471833213</v>
       </c>
       <c r="I56">
-        <v>0.9999646753182282</v>
+        <v>0.9999644375082212</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2738,19 +2738,19 @@
         </is>
       </c>
       <c r="E57">
-        <v>-0.3099739436401539</v>
+        <v>-0.3099739436401542</v>
       </c>
       <c r="F57">
-        <v>0.3828672789229722</v>
+        <v>0.3828672319048955</v>
       </c>
       <c r="G57">
-        <v>354</v>
+        <v>159.9999999999951</v>
       </c>
       <c r="H57">
-        <v>-0.8096120005661716</v>
+        <v>-0.809612099990714</v>
       </c>
       <c r="I57">
-        <v>0.9275926683496581</v>
+        <v>0.9273639444556074</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="E58">
-        <v>-0.2812771384345911</v>
+        <v>-0.2812771384345897</v>
       </c>
       <c r="F58">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048942</v>
       </c>
       <c r="G58">
-        <v>354</v>
+        <v>159.999999999997</v>
       </c>
       <c r="H58">
-        <v>-0.7346596429599301</v>
+        <v>-0.7346597331799345</v>
       </c>
       <c r="I58">
-        <v>0.9482806151142027</v>
+        <v>0.9480879122888173</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2822,19 +2822,19 @@
         </is>
       </c>
       <c r="E59">
-        <v>-0.267188167829324</v>
+        <v>-0.267188167829326</v>
       </c>
       <c r="F59">
-        <v>0.3828672789229715</v>
+        <v>0.3828672319048964</v>
       </c>
       <c r="G59">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H59">
-        <v>-0.6978610671064404</v>
+        <v>-0.6978611528073918</v>
       </c>
       <c r="I59">
-        <v>0.9568717042190821</v>
+        <v>0.9566994169186808</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2864,19 +2864,19 @@
         </is>
       </c>
       <c r="E60">
-        <v>-0.2384913626237613</v>
+        <v>-0.2384913626237615</v>
       </c>
       <c r="F60">
-        <v>0.3828672789229728</v>
+        <v>0.3828672319048953</v>
       </c>
       <c r="G60">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H60">
-        <v>-0.6229087095001979</v>
+        <v>-0.6229087859966116</v>
       </c>
       <c r="I60">
-        <v>0.9713588245718942</v>
+        <v>0.9712294247340705</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2906,19 +2906,19 @@
         </is>
       </c>
       <c r="E61">
-        <v>0.02869680520556275</v>
+        <v>0.02869680520556451</v>
       </c>
       <c r="F61">
-        <v>0.3828672789229727</v>
+        <v>0.3828672319048963</v>
       </c>
       <c r="G61">
-        <v>354</v>
+        <v>159.9999999999933</v>
       </c>
       <c r="H61">
-        <v>0.07495235760624017</v>
+        <v>0.07495236681078196</v>
       </c>
       <c r="I61">
-        <v>0.9999928283019887</v>
+        <v>0.999992779705323</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
